--- a/target/test-classes/TestData/Flipkartdata.xlsx
+++ b/target/test-classes/TestData/Flipkartdata.xlsx
@@ -1,23 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moinu\eclipse-workspace\Flipkart\src\test\resources\TestData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C81A7E7-BF3C-4515-B5B4-B883B28730DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{206FF3F8-105C-4E92-BD8A-91EA8C455EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -25,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
   <si>
     <t>SearchText</t>
   </si>
@@ -46,12 +42,16 @@
   </si>
   <si>
     <t>Camera</t>
+  </si>
+  <si>
+    <t>PASS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -363,45 +363,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="10.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>1</v>
       </c>
+      <c r="B2" t="s" s="0">
+        <v>7</v>
+      </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>2</v>
       </c>
+      <c r="B3" t="s" s="0">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>3</v>
       </c>
+      <c r="B4" t="s" s="0">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>4</v>
       </c>
+      <c r="B5" t="s" s="0">
+        <v>7</v>
+      </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>5</v>
       </c>
+      <c r="B6" t="s" s="0">
+        <v>7</v>
+      </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>6</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
